--- a/08_Bug_Reports/Bug_Report.xlsx
+++ b/08_Bug_Reports/Bug_Report.xlsx
@@ -1,34 +1,233 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ecommerce Testing\AutomationExcercise\08_Bug_Reports\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2631E90-D979-43E2-9063-879E3A08B920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bug Report" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Bug Report" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="53">
+  <si>
+    <t>Bug ID</t>
+  </si>
+  <si>
+    <t>Module</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Severity</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>Steps to Reproduce</t>
+  </si>
+  <si>
+    <t>Expected Result</t>
+  </si>
+  <si>
+    <t>Actual Result</t>
+  </si>
+  <si>
+    <t>Attachment/Proof</t>
+  </si>
+  <si>
+    <t>BUG_001</t>
+  </si>
+  <si>
+    <t>Add to cart modal buttons sometimes not clickable</t>
+  </si>
+  <si>
+    <t>Cart / UI Modal</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Chrome (Windows 10/11)</t>
+  </si>
+  <si>
+    <t>Open Products page -&gt; Add any product to cart -&gt; Modal popup appears -&gt; Try clicking “View Cart” / “Continue Shopping”</t>
+  </si>
+  <si>
+    <t>Modal buttons should always be clickable and responsive.</t>
+  </si>
+  <si>
+    <t>Sometimes modal buttons are not clickable due to overlay/iframe issue.</t>
+  </si>
+  <si>
+    <t>Open</t>
+  </si>
+  <si>
+    <t>Screenshot/Video (if available)</t>
+  </si>
+  <si>
+    <t>BUG_002</t>
+  </si>
+  <si>
+    <t>Cart page total items count does not update immediately after removing product</t>
+  </si>
+  <si>
+    <t>Cart</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Open Cart page -&gt; Remove a product -&gt; Observe cart total items or cart list</t>
+  </si>
+  <si>
+    <t>Cart count and total items should update instantly after removal</t>
+  </si>
+  <si>
+    <t>Sometimes cart count updates only after refresh.</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>BUG_003</t>
+  </si>
+  <si>
+    <t>Product search shows “Searched Products” heading even when no results are found</t>
+  </si>
+  <si>
+    <t>Products</t>
+  </si>
+  <si>
+    <t>Open Products page -&gt; Search keyword “xyz1235”</t>
+  </si>
+  <si>
+    <t>A clear message like “No products found” should be displayed.</t>
+  </si>
+  <si>
+    <t>Only heading is shown, but no clear “No results” message.</t>
+  </si>
+  <si>
+    <t>BUG_004</t>
+  </si>
+  <si>
+    <t>Cart persists after logout in some cases until page refresh</t>
+  </si>
+  <si>
+    <t>Login / Session</t>
+  </si>
+  <si>
+    <t>Login -&gt; Add product to cart -&gt; Logout -&gt; Observe cart icon/cart page without refresh</t>
+  </si>
+  <si>
+    <t>After logout, user session should clear immediately.</t>
+  </si>
+  <si>
+    <t>Sometimes cart/session appears active until manual refresh.</t>
+  </si>
+  <si>
+    <t>BUG_005</t>
+  </si>
+  <si>
+    <t>Quantity field in product details accepts invalid input (0 or negative)</t>
+  </si>
+  <si>
+    <t>Product Details</t>
+  </si>
+  <si>
+    <t>Open any product details -&gt; Enter quantity 0 or -1 -&gt; Click Add to cart</t>
+  </si>
+  <si>
+    <t>Quantity should accept only positive numbers (&gt;=1) with validation message.</t>
+  </si>
+  <si>
+    <t>Invalid quantity may be accepted without validation.</t>
+  </si>
+  <si>
+    <t>BUG_006</t>
+  </si>
+  <si>
+    <t>Quantity input field not displayed on Product Details page (intermittent)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Open Products page → Click “View Product” for any item → On Product Details page check quantity input field </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>#quantity</t>
+    </r>
+  </si>
+  <si>
+    <t>Quantity input field should always be visible and editable</t>
+  </si>
+  <si>
+    <t>Sometimes quantity field is not displayed / not found, causing failure</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.5"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,81 +245,37 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,40 +563,264 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K10"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="6" max="6" width="17.88671875" customWidth="1"/>
+    <col min="7" max="7" width="34.33203125" customWidth="1"/>
+    <col min="8" max="9" width="20.77734375" customWidth="1"/>
+    <col min="11" max="11" width="19.44140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Bug ID</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
+    <row r="1" spans="1:11">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="57.6">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="86.4">
+      <c r="A3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="86.4">
+      <c r="A4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="57.6">
+      <c r="A5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="72">
+      <c r="A6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="86.4">
+      <c r="A7" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="18">
+      <c r="A10" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
